--- a/ListaProductos.xlsx
+++ b/ListaProductos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gerorevetria/Desktop/ORT/Semestre 5/Diseño Interactivo/Obligatorio 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2955FBD-5211-0741-9E3E-4EB467930076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC2AD76-A0F7-7A48-9408-376065EFB3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17160" xr2:uid="{672D2A80-702B-0949-B570-3E2A5D85CE95}"/>
   </bookViews>
@@ -77,9 +77,6 @@
     <t>TG174- Termofusora.png</t>
   </si>
   <si>
-    <t>19050 - Colilla monocomando M-H.png</t>
-  </si>
-  <si>
     <t>CUPLA DE BRONZE</t>
   </si>
   <si>
@@ -194,16 +191,19 @@
     <t>500250 - Tubos corrugados para desagüe pluvial.png</t>
   </si>
   <si>
-    <t>4020610 - Tubo PVC línea presión.png</t>
-  </si>
-  <si>
     <t>TUBO PVC LÍNEA PRESIÓN</t>
   </si>
   <si>
     <t>TANQUES WEB TRICAPA SOPLADO - 600 L</t>
   </si>
   <si>
-    <t>TANQUE WEB TRICAPA SOPLADO 600L</t>
+    <t>Copia de 4020610 - Tubo PVC línea presión.png</t>
+  </si>
+  <si>
+    <t>TANQUE WEB TRICAPA SOPLADO 600L.png</t>
+  </si>
+  <si>
+    <t>19051 - Colilla monocomando M-H.png</t>
   </si>
 </sst>
 </file>
@@ -691,7 +691,7 @@
         <v>19051</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
@@ -703,7 +703,7 @@
         <v>6</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -711,7 +711,7 @@
         <v>5022</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
@@ -723,7 +723,7 @@
         <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -731,7 +731,7 @@
         <v>27122</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>11</v>
@@ -743,7 +743,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -751,10 +751,10 @@
         <v>431002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" s="1">
         <v>1.08</v>
@@ -763,7 +763,7 @@
         <v>30</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -771,10 +771,10 @@
         <v>449002</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" s="1">
         <v>0.49</v>
@@ -783,7 +783,7 @@
         <v>20</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -791,10 +791,10 @@
         <v>281436</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9" s="1">
         <v>97.74</v>
@@ -803,7 +803,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -811,10 +811,10 @@
         <v>47015</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="D10" s="1">
         <v>4.17</v>
@@ -823,7 +823,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -831,10 +831,10 @@
         <v>14071</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D11" s="1">
         <v>1.91</v>
@@ -843,7 +843,7 @@
         <v>10</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -851,10 +851,10 @@
         <v>13701</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D12" s="1">
         <v>7.06</v>
@@ -863,7 +863,7 @@
         <v>5</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -871,10 +871,10 @@
         <v>667001</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="D13" s="1">
         <v>11.86</v>
@@ -883,7 +883,7 @@
         <v>5</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -891,10 +891,10 @@
         <v>685001</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D14" s="1">
         <v>3.79</v>
@@ -903,7 +903,7 @@
         <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -911,10 +911,10 @@
         <v>630101</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" s="1">
         <v>3.4</v>
@@ -923,7 +923,7 @@
         <v>20</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -931,10 +931,10 @@
         <v>97254</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="D16" s="1">
         <v>26.77</v>
@@ -943,7 +943,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -951,10 +951,10 @@
         <v>97241</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" s="1">
         <v>8.69</v>
@@ -963,7 +963,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -971,10 +971,10 @@
         <v>97256</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D18" s="1">
         <v>1.41</v>
@@ -983,7 +983,7 @@
         <v>6</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -991,10 +991,10 @@
         <v>40123</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="D19" s="1">
         <v>3.53</v>
@@ -1003,7 +1003,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -1011,10 +1011,10 @@
         <v>500250</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D20" s="1">
         <v>119.97</v>
@@ -1023,7 +1023,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -1031,10 +1031,10 @@
         <v>4020610</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D21" s="1">
         <v>12.18</v>
@@ -1043,7 +1043,7 @@
         <v>5</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -1051,7 +1051,7 @@
         <v>90600</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>11</v>
@@ -1063,7 +1063,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
